--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1205,7 +1205,7 @@
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-06-09T18:53:39.513Z</v>
+        <v>2026-06-09T21:42:39.580Z</v>
       </c>
     </row>
     <row r="14">
@@ -1704,9 +1704,71 @@
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YARD-000021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>9999</v>
+      </c>
+      <c r="C22" t="str">
+        <v>12555</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Toyota</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8fgu25</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2020</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Showroom</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Section 5</v>
+      </c>
+      <c r="J22" t="str">
+        <v>B</v>
+      </c>
+      <c r="K22" t="str">
+        <v>12</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Indoor Display</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Ready</v>
+      </c>
+      <c r="O22" t="str">
+        <v>No</v>
+      </c>
+      <c r="P22" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Ethan</v>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v>2026-06-09T21:59:02.590Z</v>
+      </c>
+      <c r="T22" t="str">
+        <v>2026-06-09T21:59:02.590Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -1736,7 +1736,7 @@
         <v>B</v>
       </c>
       <c r="K22" t="str">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L22" t="str">
         <v>Indoor Display</v>
@@ -1763,7 +1763,7 @@
         <v>2026-06-09T21:59:02.590Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-06-09T21:59:02.590Z</v>
+        <v>2026-06-10T03:30:08.644Z</v>
       </c>
     </row>
   </sheetData>
